--- a/static/excel_templates/보정.xlsx
+++ b/static/excel_templates/보정.xlsx
@@ -15,7 +15,7 @@
     <sheet name="보정" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">보정!$A$1:$G$34</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">보정!$A$1:$G$30</definedName>
   </definedNames>
   <calcPr calcId="162913" calcMode="manual"/>
   <extLst>
@@ -299,10 +299,10 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -648,7 +648,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.25" style="1" customWidth="1"/>
@@ -765,7 +765,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -774,7 +774,7 @@
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
     </row>
-    <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -783,7 +783,7 @@
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
     </row>
-    <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -792,7 +792,7 @@
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
     </row>
-    <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -801,7 +801,7 @@
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
     </row>
-    <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -810,7 +810,7 @@
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
     </row>
-    <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -819,7 +819,7 @@
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
     </row>
-    <row r="18" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -828,7 +828,7 @@
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
     </row>
-    <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -836,6 +836,96 @@
       <c r="E19" s="2"/>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
+    </row>
+    <row r="20" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+    </row>
+    <row r="21" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+    </row>
+    <row r="22" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+    </row>
+    <row r="23" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+    </row>
+    <row r="24" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+    </row>
+    <row r="25" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+    </row>
+    <row r="26" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="2"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+    </row>
+    <row r="27" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="2"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+    </row>
+    <row r="28" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="2"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+    </row>
+    <row r="29" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="2"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -851,6 +941,9 @@
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="85" orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>&amp;C&amp;"-,굵게"한 국 건 설 품 질 시 험 원 (주)</oddFooter>
+  </headerFooter>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>